--- a/feedback_forms/026_design_evolution_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/026_design_evolution_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design Evolution Feedback Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction to the Design Evolution Feedback Survey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to provide your feedback on the current design evolution process.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,17 +542,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_2</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>What do you think about the current design evolution process?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +565,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_3</t>
+          <t>select_one_feedback_option</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Select one option that best describes your feedback.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_4</t>
+          <t>select_multiple_feedback_options</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Select multiple options that best describe your feedback.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_5</t>
+          <t>date_of_last_feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>When was your last feedback given?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_6</t>
+          <t>time_of_last_feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>What time was your last feedback given?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_7</t>
+          <t>design_preferences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design Evolution Feedback Survey</t>
+          <t>What type of design preferences do you have for the current design evolution process?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,15 +685,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_8</t>
+          <t>demographic_information</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design Evolution Feedback Survey</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Demographic Information</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide your demographic information for analysis purposes.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -707,12 +715,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,85 +743,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_2_choices</t>
+          <t>select_one_feedback_option_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'feedback'}</t>
+          <t>the_design_evolution_process_is_well-organized_and_structured.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Feedback'}</t>
+          <t>The design evolution process is well-organized and structured.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_2_choices</t>
+          <t>select_one_feedback_option_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'feedback_2'}</t>
+          <t>the_design_evolution_process_is_disorganized_and_unstructured.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Feedback 2'}</t>
+          <t>The design evolution process is disorganized and unstructured.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_3_choices</t>
+          <t>select_one_feedback_option_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'feedback'}</t>
+          <t>i'm_not_sure.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Feedback'}</t>
+          <t>I'm not sure.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_3_choices</t>
+          <t>select_multiple_feedback_options_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'feedback_1'}</t>
+          <t>the_design_evolution_process_is_well-organized_and_structured.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Feedback 1'}</t>
+          <t>The design evolution process is well-organized and structured.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>design_evolution_feedback_survey_page_3_choices</t>
+          <t>select_multiple_feedback_options_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'feedback_2'}</t>
+          <t>the_design_evolution_process_is_disorganized_and_unstructured.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Feedback 2'}</t>
+          <t>The design evolution process is disorganized and unstructured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>select_multiple_feedback_options_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>i'm_not_sure.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>I'm not sure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>design_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>simple_and_intuitive_design.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Simple and intuitive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>design_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>complex_and_detailed_design.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Complex and detailed design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>design_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>customizable_design.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Customizable design.</t>
         </is>
       </c>
     </row>
